--- a/reports/tableau-suivi.xlsx
+++ b/reports/tableau-suivi.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="270" documentId="11_F9C8E750BC5A4780F0AC0B6737F18CEE6FB2ED55" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEC17C80-16CA-4C7E-8A07-1EABA4B085B7}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="11_F9C8E750BC5A4780F0AC0B6737F18CEE6FB2ED55" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E14F15CB-EDE7-4026-94A0-47CF5F963534}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="192">
   <si>
     <t>Accepté</t>
   </si>
@@ -444,9 +444,6 @@
     <t>3DS</t>
   </si>
   <si>
-    <t>chef de projet IA Graduate</t>
-  </si>
-  <si>
     <t>https://www.3ds.com/fr/careers/jobs/chef-de-projet-data-ia-et-transformation-voyages-d-affaires-f-h-547581</t>
   </si>
   <si>
@@ -501,19 +498,115 @@
     <t>C:\Users\HamzaRIABI\OneDrive - STARTUM CFA\Bureau\JOB\cv-gen\output\wavestone-consultant-e-junior-ia-data-ag-2026-05-20</t>
   </si>
   <si>
-    <t>Wavestone</t>
-  </si>
-  <si>
-    <t>26/05/2026 13:15</t>
-  </si>
-  <si>
-    <t>Consultant·e Data - Secteur Public</t>
-  </si>
-  <si>
-    <t>https://jobs.smartrecruiters.com/Wavestone1/744000097717820-cdi-consultant%c2%b7e-data-secteur-public</t>
-  </si>
-  <si>
-    <t>C:\Users\HamzaRIABI\OneDrive - STARTUM CFA\Bureau\JOB\cv-gen\output\wavestone-consultant-e-data-secteur-publ-2026-05-26</t>
+    <t>ENGIE</t>
+  </si>
+  <si>
+    <t>29/05/2026 18:34</t>
+  </si>
+  <si>
+    <t>S&amp;EM Young Graduate Program - IT Business Analyst</t>
+  </si>
+  <si>
+    <t>https://jobs.engie.com/job/S&amp;EM-Young-Graduate-Program-IT-Business-Analyst/64910-en_US/?utm_campaign=auto__src%3Ana%7Cmed%3Ana%7Cref%3Adirect</t>
+  </si>
+  <si>
+    <t>En cours</t>
+  </si>
+  <si>
+    <t>C:\Users\HamzaRIABI\OneDrive - STARTUM CFA\Bureau\JOB\cv-gen\output\non-sp-cifi-e-non-sp-cifi-e-2026-05-29</t>
+  </si>
+  <si>
+    <t>Pharmacos</t>
+  </si>
+  <si>
+    <t>Responsable Support Opérationnel Systèmes Essais Cliniques</t>
+  </si>
+  <si>
+    <t>https://dauphine.jobteaser.com/fr/job-offers/f4c9c593-c5d0-422b-aa7a-61dba699ed9b-house-of-aby-data-manager-validation-de-systeme-x-f-h</t>
+  </si>
+  <si>
+    <t>C:\Users\HamzaRIABI\OneDrive - STARTUM CFA\Bureau\JOB\cv-gen\output\pharmacos-responsable-support-op-rationn-2026-05-29</t>
+  </si>
+  <si>
+    <t>29/05/2026 22:18</t>
+  </si>
+  <si>
+    <t>https://dauphine.jobteaser.com/fr/job-offers/faeac9cd-e3c3-4718-8cdc-3c1765fceee1-bearingpoint-consultant-junior-tech-data-h-f</t>
+  </si>
+  <si>
+    <t>C:\Users\HamzaRIABI\OneDrive - STARTUM CFA\Bureau\JOB\cv-gen\output\non-sp-cifi-e-non-sp-cifi-2026-05-29</t>
+  </si>
+  <si>
+    <t>29/05/2026 22:37</t>
+  </si>
+  <si>
+    <t>BearingPoint</t>
+  </si>
+  <si>
+    <t>https://dauphine.jobteaser.com/fr/job-offers/a66d53fd-4349-411b-87cb-803c16a59c5b-bearingpoint-analyste-a-consultant-it-tech-m-a-h-f</t>
+  </si>
+  <si>
+    <t>Analyste à Consultant IT/Tech M&amp;A (H/F)</t>
+  </si>
+  <si>
+    <t>Consultant Junior Tech &amp; Data &amp; Cyber (H/F)</t>
+  </si>
+  <si>
+    <t>Cabinet Advisory (Non spécifié)</t>
+  </si>
+  <si>
+    <t>29/05/2026 23:59</t>
+  </si>
+  <si>
+    <t>Data Analyst (H/F)</t>
+  </si>
+  <si>
+    <t>https://careers.cbre.com/en_US/careers/JobDetail/Data-Analyst-H-F/277228?source=JobTeaser%20(Standard%20Job%20Ad)</t>
+  </si>
+  <si>
+    <t>C:\Users\HamzaRIABI\OneDrive - STARTUM CFA\Bureau\JOB\cv-gen\output\cabinet-advisory-non-sp-cifi-data-analyst-h-f-2026-05-29</t>
+  </si>
+  <si>
+    <t>Consultant(e) Junior ✏️ - LUXE - Transformation Digitale - CDI - PARIS - Missions &amp; déplacements en Europe</t>
+  </si>
+  <si>
+    <t>DataValue Strategy</t>
+  </si>
+  <si>
+    <t>https://dauphine.jobteaser.com/fr/job-offers/01a0c1d5-e596-4362-be8d-960474441560-datavalue-strategy-consultant-e-junior-luxe-transformation-digitale-cdi-paris-missions-deplacements-en-europe</t>
+  </si>
+  <si>
+    <t>Chef de projet Data IA et Transformation - Voyages d’affaires (F/H) GRADUATE</t>
+  </si>
+  <si>
+    <t>faut penser comment entregistrer les appels</t>
+  </si>
+  <si>
+    <t>Deloitte France</t>
+  </si>
+  <si>
+    <t>02/06/2026 01:20</t>
+  </si>
+  <si>
+    <t>https://www.deloitte.com/fr/fr/careers/content/job/results/offer.html?ref=R-8886</t>
+  </si>
+  <si>
+    <t>C:\Users\HamzaRIABI\OneDrive - STARTUM CFA\Bureau\JOB\cv-gen\output\deloitte-france-data-analyst-analytics-enginee-2026-06-01</t>
+  </si>
+  <si>
+    <t>Consultant Audit Analytics F/H</t>
+  </si>
+  <si>
+    <t>https://www.deloitte.com/fr/fr/careers/content/job/results/offer.html?ref=R-6900</t>
+  </si>
+  <si>
+    <t>Consultant junior Data Analyst – Spécialiste data quality et data Gouvernance (F/H</t>
+  </si>
+  <si>
+    <t>Consultant Risk Data Analyst / Data Scientist F/H</t>
+  </si>
+  <si>
+    <t>https://www.deloitte.com/fr/fr/careers/content/job/results/offer.html?ref=R-8758</t>
   </si>
 </sst>
 </file>
@@ -741,13 +834,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -847,9 +940,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1925292</xdr:colOff>
+      <xdr:colOff>1921482</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>630224</xdr:rowOff>
+      <xdr:rowOff>626414</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1146,23 +1239,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:W60"/>
+  <dimension ref="A2:W68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.44140625" customWidth="1"/>
     <col min="2" max="2" width="37.109375" customWidth="1"/>
     <col min="3" max="3" width="37.6640625" customWidth="1"/>
-    <col min="4" max="4" width="39" customWidth="1"/>
+    <col min="4" max="4" width="81.88671875" customWidth="1"/>
     <col min="5" max="5" width="158.88671875" customWidth="1"/>
     <col min="6" max="6" width="26.6640625" customWidth="1"/>
     <col min="7" max="7" width="18.44140625" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="39.109375" customWidth="1"/>
     <col min="9" max="9" width="135.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E2" s="1">
-        <f>COUNTIF($F$9:$F$998,"Accepté")</f>
+        <f>COUNTIF($F$9:$F$996,"Accepté")</f>
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1171,8 +1264,8 @@
     </row>
     <row r="3" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E3" s="1">
-        <f>COUNTIF($F$9:$F$998,"Refusé")</f>
-        <v>6</v>
+        <f>COUNTIF($F$9:$F$996,"Refusé")</f>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>1</v>
@@ -1180,7 +1273,7 @@
     </row>
     <row r="4" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E4" s="1">
-        <f>COUNTIF($F$9:$F$998,"À envoyer")</f>
+        <f>COUNTIF($F$9:$F$996,"À envoyer")</f>
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1189,8 +1282,8 @@
     </row>
     <row r="5" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E5" s="1">
-        <f>COUNTIF($F$9:$F$998,"Postulé")</f>
-        <v>46</v>
+        <f>COUNTIF($F$9:$F$996,"Postulé")</f>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -1254,7 +1347,7 @@
         <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I9" t="s">
         <v>32</v>
@@ -1418,7 +1511,7 @@
         <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
@@ -1441,7 +1534,7 @@
         <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
         <v>41</v>
@@ -1786,7 +1879,7 @@
         <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I32" t="s">
         <v>109</v>
@@ -1809,7 +1902,7 @@
         <v>118</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I33" t="s">
         <v>119</v>
@@ -1918,16 +2011,22 @@
         <v>46164.718055555553</v>
       </c>
       <c r="D38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="F38" t="s">
+        <v>159</v>
+      </c>
+      <c r="G38">
+        <v>33161624156</v>
+      </c>
+      <c r="H38" t="s">
+        <v>182</v>
+      </c>
+      <c r="I38" t="s">
         <v>138</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -1935,22 +2034,22 @@
         <v>31</v>
       </c>
       <c r="B39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" t="s">
         <v>140</v>
       </c>
-      <c r="C39" t="s">
-        <v>143</v>
-      </c>
-      <c r="D39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" t="s">
         <v>141</v>
-      </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1958,22 +2057,22 @@
         <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C40" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
       </c>
       <c r="I40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1981,22 +2080,22 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C41" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F41" t="s">
         <v>13</v>
       </c>
       <c r="I41" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2004,22 +2103,22 @@
         <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C42" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F42" t="s">
         <v>13</v>
       </c>
       <c r="I42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2027,22 +2126,22 @@
         <v>35</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C43" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F43" t="s">
         <v>13</v>
       </c>
       <c r="I43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2050,22 +2149,22 @@
         <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C44" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F44" t="s">
         <v>13</v>
       </c>
       <c r="I44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2073,22 +2172,22 @@
         <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C45" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D45" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F45" t="s">
         <v>13</v>
       </c>
       <c r="I45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2096,22 +2195,22 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C46" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" t="s">
         <v>13</v>
       </c>
       <c r="I46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2119,22 +2218,22 @@
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C47" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
         <v>13</v>
       </c>
       <c r="I47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2142,22 +2241,22 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C48" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" t="s">
         <v>13</v>
       </c>
       <c r="I48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2165,22 +2264,22 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C49" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F49" t="s">
         <v>13</v>
       </c>
       <c r="I49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2188,22 +2287,22 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C50" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D50" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E50" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="F50" t="s">
         <v>13</v>
       </c>
       <c r="I50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2211,22 +2310,22 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D51" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="F51" t="s">
         <v>13</v>
       </c>
       <c r="I51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2234,22 +2333,22 @@
         <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C52" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D52" t="s">
+        <v>153</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" t="s">
         <v>154</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F52" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2257,22 +2356,22 @@
         <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F53" t="s">
         <v>13</v>
       </c>
       <c r="I53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2280,22 +2379,22 @@
         <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C54" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F54" t="s">
         <v>13</v>
       </c>
       <c r="I54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2303,22 +2402,22 @@
         <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F55" t="s">
         <v>13</v>
       </c>
       <c r="I55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2326,22 +2425,22 @@
         <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C56" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F56" t="s">
         <v>13</v>
       </c>
       <c r="I56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2349,22 +2448,22 @@
         <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C57" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F57" t="s">
         <v>13</v>
       </c>
       <c r="I57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2372,22 +2471,22 @@
         <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C58" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F58" t="s">
         <v>13</v>
       </c>
       <c r="I58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2395,22 +2494,22 @@
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C59" s="10">
         <v>46165.017361111109</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
       </c>
       <c r="I59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -2418,31 +2517,215 @@
         <v>52</v>
       </c>
       <c r="B60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60" t="s">
         <v>156</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>157</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>158</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>159</v>
-      </c>
-      <c r="F60" t="s">
-        <v>13</v>
       </c>
       <c r="I60" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>53</v>
+      </c>
+      <c r="B61" t="s">
+        <v>161</v>
+      </c>
+      <c r="C61" t="s">
+        <v>165</v>
+      </c>
+      <c r="D61" t="s">
+        <v>162</v>
+      </c>
+      <c r="E61" t="s">
+        <v>163</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>54</v>
+      </c>
+      <c r="B62" t="s">
+        <v>169</v>
+      </c>
+      <c r="C62" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" t="s">
+        <v>172</v>
+      </c>
+      <c r="E62" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>55</v>
+      </c>
+      <c r="B63" t="s">
+        <v>169</v>
+      </c>
+      <c r="C63" t="s">
+        <v>168</v>
+      </c>
+      <c r="D63" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1</v>
+      </c>
+      <c r="I63" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>56</v>
+      </c>
+      <c r="B64" t="s">
+        <v>173</v>
+      </c>
+      <c r="C64" t="s">
+        <v>174</v>
+      </c>
+      <c r="D64" t="s">
+        <v>175</v>
+      </c>
+      <c r="E64" t="s">
+        <v>176</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>57</v>
+      </c>
+      <c r="B65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" s="10">
+        <v>46173.730555555558</v>
+      </c>
+      <c r="D65" t="s">
+        <v>178</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F65" t="s">
+        <v>13</v>
+      </c>
+      <c r="I65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>58</v>
+      </c>
+      <c r="B66" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" t="s">
+        <v>187</v>
+      </c>
+      <c r="E66" t="s">
+        <v>185</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>59</v>
+      </c>
+      <c r="B67" t="s">
+        <v>183</v>
+      </c>
+      <c r="C67" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" t="s">
+        <v>189</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1</v>
+      </c>
+      <c r="I67" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>60</v>
+      </c>
+      <c r="B68" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" t="s">
+        <v>184</v>
+      </c>
+      <c r="D68" t="s">
+        <v>190</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F208:F303" xr:uid="{D1E0F792-6E12-4B8A-8F9C-407C0C0946D7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F206:F301" xr:uid="{D1E0F792-6E12-4B8A-8F9C-407C0C0946D7}">
       <formula1>"À envoyer,En cours,Postulé,Refusé"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F207" xr:uid="{B8D8C9B5-ECBD-4401-B383-348793B2F263}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F205" xr:uid="{B8D8C9B5-ECBD-4401-B383-348793B2F263}">
       <formula1>"À envoyer,En cours,Postulé,Refusé,Accepté"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2469,9 +2752,13 @@
     <hyperlink ref="E52" r:id="rId20" xr:uid="{7D752D8A-2859-408E-BC7F-7F140AE81D5C}"/>
     <hyperlink ref="E50:E51" r:id="rId21" display="https://jobs.smartrecruiters.com/Wavestone1/744000123735818-consultant%c2%b7e-ai-data-platform-jeune-diplome%c2%b7e-h-f" xr:uid="{418F17E0-2780-4245-980B-74D99137D6C1}"/>
     <hyperlink ref="E53:E59" r:id="rId22" display="https://jobs.smartrecruiters.com/Wavestone1/744000120709675-ai-engineer" xr:uid="{0EC1A1A0-77B1-4FDE-A550-4968D01669A2}"/>
+    <hyperlink ref="E63" r:id="rId23" xr:uid="{D4DE81B4-6E54-4973-9BF3-5E26D1EFCC70}"/>
+    <hyperlink ref="E65" r:id="rId24" xr:uid="{B8339229-61A5-4AED-A003-649ED8D34C2B}"/>
+    <hyperlink ref="E67" r:id="rId25" xr:uid="{1BAAF2FF-F4DD-409B-A974-EC6F5927FB3E}"/>
+    <hyperlink ref="E68" r:id="rId26" xr:uid="{BBEE684F-8D8C-4D6A-9D0C-E05E15B88A83}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
-  <drawing r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>